--- a/Estimation/IPC-Migration-Programme-Estimate.xlsx
+++ b/Estimation/IPC-Migration-Programme-Estimate.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Options &amp; Exclusions" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rate Card &amp; Commercials" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -244,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -400,6 +401,9 @@
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,6 +478,1610 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Programme Gantt by phase — 76 weeks</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!AE4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$AD$5:$AD$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$AE$5:$AE$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!AF4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8C7A5B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8C7A5B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9A6A4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9A6A4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F6B7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F6B7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="6B6459"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="6B6459"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="D6D3D1"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="D6D3D1"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B6E4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B6E4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7A5B6B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7A5B6B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F5F7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F5F7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="6B6459"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="6B6459"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <cat>
+            <numRef>
+              <f>'Charts'!$AD$5:$AD$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$AF$5:$AF$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="76"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Programme week</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Work package Gantt — 49 packages</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!AE15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$AD$16:$AD$64</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$AE$16:$AE$64</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!AF15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8C7A5B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8C7A5B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="6B6459"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="6B6459"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8C7A5B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8C7A5B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="6B6459"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="6B6459"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8C7A5B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8C7A5B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9A6A4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9A6A4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9A6A4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9A6A4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F6B7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F6B7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F6B7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F6B7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="9"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8C7A5B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8C7A5B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="10"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8C7A5B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8C7A5B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="11"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9A6A4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9A6A4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="12"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8C7A5B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8C7A5B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="13"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9A6A4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9A6A4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="14"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9A6A4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9A6A4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="15"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F6B7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F6B7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="16"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8C7A5B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="8C7A5B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="17"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9A6A4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="9A6A4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="18"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F6B7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F6B7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="19"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F6B7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F6B7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="20"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F6B7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F6B7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="21"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F6B7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F6B7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="22"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F6B7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F6B7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="23"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F6B7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F6B7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="24"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="6B6459"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="6B6459"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="25"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B6E4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B6E4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="26"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="6B6459"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="6B6459"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="27"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="6B6459"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="6B6459"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="28"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B6E4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B6E4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="29"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B6E4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B6E4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="30"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B6E4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B6E4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="31"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B6E4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B6E4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="32"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B6E4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B6E4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="33"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B6E4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B6E4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="34"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B6E4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B6E4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="35"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B6E4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B6E4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="36"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B6E4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B6E4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="37"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="5B6E4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="5B6E4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="38"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7A5B6B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7A5B6B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="39"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7A5B6B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7A5B6B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="40"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7A5B6B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7A5B6B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="41"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F5F7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F5F7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="42"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7A5B6B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7A5B6B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="43"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7A5B6B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7A5B6B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="44"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="6B6459"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="6B6459"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="45"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F5F7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F5F7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="46"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F5F7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F5F7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="47"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F5F7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F5F7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="48"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F5F7A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4F5F7A"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <cat>
+            <numRef>
+              <f>'Charts'!$AD$16:$AD$64</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$AF$16:$AF$64</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="76"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Programme week</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Resource loading — person-days by role, 19 four-week periods (divide by 20 for FTE)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!AD71</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4F6B7A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$AE$70:$AW$70</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$AE$71:$AW$71</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!AD72</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="8C7A5B"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$AE$70:$AW$70</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$AE$72:$AW$72</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!AD73</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="9A6A4F"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$AE$70:$AW$70</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$AE$73:$AW$73</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!AD74</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="5B6E4F"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$AE$70:$AW$70</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$AE$74:$AW$74</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!AD75</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="7A5B6B"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$AE$70:$AW$70</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$AE$75:$AW$75</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!AD76</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="6B6459"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$AE$70:$AW$70</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$AE$76:$AW$76</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!AD77</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4F5F7A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$AE$70:$AW$70</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$AE$77:$AW$77</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!AD78</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="A88B4A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$AE$70:$AW$70</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$AE$78:$AW$78</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Four-week period</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Person-days in period</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Team size — full-time equivalents by period</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!AD79</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Charts'!$AE$70:$AW$70</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$AE$79:$AW$79</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Four-week period</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>FTE</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10800000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10800000" cy="12240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>97</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10800000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>123</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10800000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -765,7 +2373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -958,125 +2566,137 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Four live Excel charts: a phase-level Gantt, a package-level Gantt across all 49 packages, resource loading stacked by role, and team size in FTE. Their backing data sits to the right in column AD — edit it and the charts move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>UNITS</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>PD — person-day</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>One person for one day. 21 PD make a person-month; 20 PD make one four-week period at five days a week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>P80</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Four engagements in five finish at or below this effort. The standard basis for a fixed-price government contract. P50 is even odds and should never be bid.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>INR lakh</t>
+          <t>P80</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>One hundred thousand rupees. Payment values are given in full rupees so they can be transcribed into a purchase order.</t>
+          <t>Four engagements in five finish at or below this effort. The standard basis for a fixed-price government contract. P50 is even odds and should never be bid.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>INR lakh</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>One hundred thousand rupees. Payment values are given in full rupees so they can be transcribed into a purchase order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
           <t>Ex-GST / inc-GST</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Contract value before and after GST at 18%. Verify whether IPC can claim input credit as an autonomous body — if not, GST is a real cost to the buyer.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>THREE THINGS TO SETTLE BEFORE SIGNING</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Supplier tier</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>This price assumes a boutique or specialist supplier. IPC's own last IT tender (GEM/2026/B/7781379, 13-07-2026) demanded ISO 9001, ISO 27000 and CMMI Level 3 — a bar that excludes that tier. At mid-tier rates Stage 1 is roughly INR 33 lakh. Resolve the procurement category before bidding, not at evaluation.</t>
-        </is>
-      </c>
+      <c r="B28" s="4" t="inlineStr"/>
     </row>
     <row r="29" ht="45" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>Supplier tier</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>This price assumes a boutique or specialist supplier. IPC's own last IT tender (GEM/2026/B/7781379, 13-07-2026) demanded ISO 9001, ISO 27000 and CMMI Level 3 — a bar that excludes that tier. At mid-tier rates Stage 1 is roughly INR 33 lakh. Resolve the procurement category before bidding, not at evaluation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t>How much content survives</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>The destination has no bulk import, and MoHFW — IPC's own ministry — carried across 28 pages and no documents at all. Against IPC's 1,084 items and 2,758 PDFs, triage is the whole project rather than a tidying step. This single answer swings the options by hundreds of person-days.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Performance guarantee term</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>IPC's revealed ePBG was 5% held for 60 months. On a 24-week assignment that is a five-year guarantee against a six-month job. Negotiate the term, not only the rate.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="45" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>WHAT MOVED IN THE SCHEDULE</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Phase 2 starts in week 3, in parallel with Phase 1 rather than after it. The 302-to-404 behaviour measured on 2026-09-01 is a usable existence oracle, so the inventory is not blocked on the 404 fix — which removes roughly six weeks from the plan's original sequencing.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="75" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="34" ht="75" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>THE GAP BETWEEN STAGES</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Stage 2 cannot be procured until Stage 1 delivers the baseline that makes it costable. Twelve weeks is the planning figure for that gap: IPC's last bid ran 11 days from publication to close, but carried 180 days of bid validity, and the governance chain — Secretary, then Chairman of the Governing Body, then the Governing Body — is the long pole. Range 8 to 16 weeks. This gap is where programmes lose time, so it is drawn rather than hidden.</t>
         </is>
@@ -1642,6 +3262,1534 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AW79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="9" customWidth="1" min="32" max="32"/>
+    <col width="9" customWidth="1" min="33" max="33"/>
+    <col width="9" customWidth="1" min="34" max="34"/>
+    <col width="9" customWidth="1" min="35" max="35"/>
+    <col width="9" customWidth="1" min="36" max="36"/>
+    <col width="9" customWidth="1" min="37" max="37"/>
+    <col width="9" customWidth="1" min="38" max="38"/>
+    <col width="9" customWidth="1" min="39" max="39"/>
+    <col width="9" customWidth="1" min="40" max="40"/>
+    <col width="9" customWidth="1" min="41" max="41"/>
+    <col width="9" customWidth="1" min="42" max="42"/>
+    <col width="9" customWidth="1" min="43" max="43"/>
+    <col width="9" customWidth="1" min="44" max="44"/>
+    <col width="9" customWidth="1" min="45" max="45"/>
+    <col width="9" customWidth="1" min="46" max="46"/>
+    <col width="9" customWidth="1" min="47" max="47"/>
+    <col width="9" customWidth="1" min="48" max="48"/>
+    <col width="9" customWidth="1" min="49" max="49"/>
+    <col width="9" customWidth="1" min="50" max="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Live Excel charts driven by the data blocks below them. The Gantt is a stacked bar whose first series is invisible — that series carries the start week, the second carries the duration. Edit a number in the block and the chart moves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="AC4" s="87" t="inlineStr">
+        <is>
+          <t>Chart data →</t>
+        </is>
+      </c>
+      <c r="AD4" s="73" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="AE4" s="73" t="inlineStr">
+        <is>
+          <t>Start-1</t>
+        </is>
+      </c>
+      <c r="AF4" s="73" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="AD5" s="44" t="inlineStr">
+        <is>
+          <t>Stage 1 · 0 · Mandate and decisions</t>
+        </is>
+      </c>
+      <c r="AE5" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="44" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="AD6" s="44" t="inlineStr">
+        <is>
+          <t>Stage 1 · 1 · Emergency remediation</t>
+        </is>
+      </c>
+      <c r="AE6" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" s="44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="AD7" s="44" t="inlineStr">
+        <is>
+          <t>Stage 1 · 2 · Inventory and redirect map</t>
+        </is>
+      </c>
+      <c r="AE7" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF7" s="44" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="AD8" s="44" t="inlineStr">
+        <is>
+          <t>Stage 1 · P · Programme management</t>
+        </is>
+      </c>
+      <c r="AE8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="44" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="AD9" s="44" t="inlineStr">
+        <is>
+          <t>Procurement gap</t>
+        </is>
+      </c>
+      <c r="AE9" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF9" s="44" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="AD10" s="44" t="inlineStr">
+        <is>
+          <t>Stage 2 · 3 · Build and content load</t>
+        </is>
+      </c>
+      <c r="AE10" s="44" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF10" s="44" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="AD11" s="44" t="inlineStr">
+        <is>
+          <t>Stage 2 · 4 · Audit and clearance</t>
+        </is>
+      </c>
+      <c r="AE11" s="44" t="n">
+        <v>53</v>
+      </c>
+      <c r="AF11" s="44" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="AD12" s="44" t="inlineStr">
+        <is>
+          <t>Stage 2 · 5 · Cut-over and hypercare</t>
+        </is>
+      </c>
+      <c r="AE12" s="44" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF12" s="44" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="AD13" s="44" t="inlineStr">
+        <is>
+          <t>Stage 2 · P · Programme management</t>
+        </is>
+      </c>
+      <c r="AE13" s="44" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF13" s="44" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="AD15" s="73" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="AE15" s="73" t="inlineStr">
+        <is>
+          <t>Start-1</t>
+        </is>
+      </c>
+      <c r="AF15" s="73" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="AD16" s="44" t="inlineStr">
+        <is>
+          <t>0.1 Correct the brief; re-issue the objective in</t>
+        </is>
+      </c>
+      <c r="AE16" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="AD17" s="44" t="inlineStr">
+        <is>
+          <t>P.1a Programme and delivery management — Stage 1</t>
+        </is>
+      </c>
+      <c r="AE17" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="44" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="AD18" s="44" t="inlineStr">
+        <is>
+          <t>0.2 Gov.In CMS intake via the MoHFW CIO route</t>
+        </is>
+      </c>
+      <c r="AE18" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="44" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="AD19" s="44" t="inlineStr">
+        <is>
+          <t>P.2a Business analysis and content governance — S</t>
+        </is>
+      </c>
+      <c r="AE19" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="44" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="AD20" s="44" t="inlineStr">
+        <is>
+          <t>0.6 Redirect-capability determination (pivotal)</t>
+        </is>
+      </c>
+      <c r="AE20" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" s="44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="AD21" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1 Real HTTP 404: error-document status, not a </t>
+        </is>
+      </c>
+      <c r="AE21" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF21" s="44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="AD22" s="44" t="inlineStr">
+        <is>
+          <t>1.2 Charset: header says iso-8859-1 over 389 Hin</t>
+        </is>
+      </c>
+      <c r="AE22" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF22" s="44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="AD23" s="44" t="inlineStr">
+        <is>
+          <t>2.1 Joomla database extraction and reconciliatio</t>
+        </is>
+      </c>
+      <c r="AE23" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF23" s="44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="AD24" s="44" t="inlineStr">
+        <is>
+          <t>2.2 Live crawl with the two-signal validator</t>
+        </is>
+      </c>
+      <c r="AE24" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF24" s="44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="AD25" s="44" t="inlineStr">
+        <is>
+          <t>0.4 registry.gov.in control and DNS readiness</t>
+        </is>
+      </c>
+      <c r="AE25" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF25" s="44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="AD26" s="44" t="inlineStr">
+        <is>
+          <t>0.9 Destination status-code behaviour proven; or</t>
+        </is>
+      </c>
+      <c r="AE26" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF26" s="44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="AD27" s="44" t="inlineStr">
+        <is>
+          <t>1.7 CSP hardening on the live site</t>
+        </is>
+      </c>
+      <c r="AE27" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF27" s="44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AD28" s="44" t="inlineStr">
+        <is>
+          <t>0.5 Security-audit route settled in writing</t>
+        </is>
+      </c>
+      <c r="AE28" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF28" s="44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AD29" s="44" t="inlineStr">
+        <is>
+          <t>1.4 GIGW policy pages and portal links (DBIM man</t>
+        </is>
+      </c>
+      <c r="AE29" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF29" s="44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="AD30" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.8 lang="hi" across 389 Hindi pages; close the </t>
+        </is>
+      </c>
+      <c r="AE30" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF30" s="44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="AD31" s="44" t="inlineStr">
+        <is>
+          <t>2.3 Wayback / CommonCrawl orphan recovery</t>
+        </is>
+      </c>
+      <c r="AE31" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF31" s="44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="AD32" s="44" t="inlineStr">
+        <is>
+          <t>0.8 DBIM logo lockup 3A/3B determination</t>
+        </is>
+      </c>
+      <c r="AE32" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF32" s="44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="AD33" s="44" t="inlineStr">
+        <is>
+          <t>1.6 robots.txt and a stopgap sitemap</t>
+        </is>
+      </c>
+      <c r="AE33" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF33" s="44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="AD34" s="44" t="inlineStr">
+        <is>
+          <t>2.4 Search Console traffic overlay</t>
+        </is>
+      </c>
+      <c r="AE34" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF34" s="44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="AD35" s="44" t="inlineStr">
+        <is>
+          <t>2.5 Union of four sources into one authoritative</t>
+        </is>
+      </c>
+      <c r="AE35" s="44" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF35" s="44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="AD36" s="44" t="inlineStr">
+        <is>
+          <t>2.9 Hindi pairing by hreflang; bilingual gap qua</t>
+        </is>
+      </c>
+      <c r="AE36" s="44" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF36" s="44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="AD37" s="44" t="inlineStr">
+        <is>
+          <t>2.6 Triage facilitation — keep / archive / retir</t>
+        </is>
+      </c>
+      <c r="AE37" s="44" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF37" s="44" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="AD38" s="44" t="inlineStr">
+        <is>
+          <t>2.7 PDF estate inventory and disposition (~2,758</t>
+        </is>
+      </c>
+      <c r="AE38" s="44" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF38" s="44" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="AD39" s="44" t="inlineStr">
+        <is>
+          <t>2.8 Redirect map — ~1,727 distinct source paths;</t>
+        </is>
+      </c>
+      <c r="AE39" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF39" s="44" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="AD40" s="44" t="inlineStr">
+        <is>
+          <t>P.3a Documentation, SOPs and the Stage 2 cost bas</t>
+        </is>
+      </c>
+      <c r="AE40" s="44" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF40" s="44" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="AD41" s="44" t="inlineStr">
+        <is>
+          <t>3.1 IA re-expression into the platform's flat st</t>
+        </is>
+      </c>
+      <c r="AE41" s="44" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF41" s="44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="AD42" s="44" t="inlineStr">
+        <is>
+          <t>P.1b Programme and delivery management — Stage 2</t>
+        </is>
+      </c>
+      <c r="AE42" s="44" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF42" s="44" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="AD43" s="44" t="inlineStr">
+        <is>
+          <t>P.2b Business analysis and content governance — S</t>
+        </is>
+      </c>
+      <c r="AE43" s="44" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF43" s="44" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="AD44" s="44" t="inlineStr">
+        <is>
+          <t>3.3 Platform configuration, roles, editorial wor</t>
+        </is>
+      </c>
+      <c r="AE44" s="44" t="n">
+        <v>37</v>
+      </c>
+      <c r="AF44" s="44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="AD45" s="44" t="inlineStr">
+        <is>
+          <t>3.2 Template mapping and the CCPS banner slot</t>
+        </is>
+      </c>
+      <c r="AE45" s="44" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF45" s="44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="AD46" s="44" t="inlineStr">
+        <is>
+          <t>3.11 Applications disposition — scoping only</t>
+        </is>
+      </c>
+      <c r="AE46" s="44" t="n">
+        <v>39</v>
+      </c>
+      <c r="AF46" s="44" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="AD47" s="44" t="inlineStr">
+        <is>
+          <t>3.4 Content mapping, authoring supervision and Q</t>
+        </is>
+      </c>
+      <c r="AE47" s="44" t="n">
+        <v>41</v>
+      </c>
+      <c r="AF47" s="44" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="AD48" s="44" t="inlineStr">
+        <is>
+          <t>3.7 Document register: categorisation scheme, pr</t>
+        </is>
+      </c>
+      <c r="AE48" s="44" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF48" s="44" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="AD49" s="44" t="inlineStr">
+        <is>
+          <t>3.9 Accessibility conformance — 9 templates, one</t>
+        </is>
+      </c>
+      <c r="AE49" s="44" t="n">
+        <v>45</v>
+      </c>
+      <c r="AF49" s="44" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="AD50" s="44" t="inlineStr">
+        <is>
+          <t>3.5 Content load — Hindi, byte-verified</t>
+        </is>
+      </c>
+      <c r="AE50" s="44" t="n">
+        <v>47</v>
+      </c>
+      <c r="AF50" s="44" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="AD51" s="44" t="inlineStr">
+        <is>
+          <t>3.10 Search configuration and relevance</t>
+        </is>
+      </c>
+      <c r="AE51" s="44" t="n">
+        <v>49</v>
+      </c>
+      <c r="AF51" s="44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="AD52" s="44" t="inlineStr">
+        <is>
+          <t>3.12 .सरकार.भारत IDN registration and configurati</t>
+        </is>
+      </c>
+      <c r="AE52" s="44" t="n">
+        <v>51</v>
+      </c>
+      <c r="AF52" s="44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="AD53" s="44" t="inlineStr">
+        <is>
+          <t>3.14 Editorial training and standard operating pr</t>
+        </is>
+      </c>
+      <c r="AE53" s="44" t="n">
+        <v>51</v>
+      </c>
+      <c r="AF53" s="44" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="AD54" s="44" t="inlineStr">
+        <is>
+          <t>4.2 Auditor procurement and pre-audit paperwork</t>
+        </is>
+      </c>
+      <c r="AE54" s="44" t="n">
+        <v>53</v>
+      </c>
+      <c r="AF54" s="44" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="AD55" s="44" t="inlineStr">
+        <is>
+          <t>4.1 Pre-audit hardening and pre-clearance of the</t>
+        </is>
+      </c>
+      <c r="AE55" s="44" t="n">
+        <v>56</v>
+      </c>
+      <c r="AF55" s="44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="AD56" s="44" t="inlineStr">
+        <is>
+          <t>4.3 VAPT cycle 1 and remediation</t>
+        </is>
+      </c>
+      <c r="AE56" s="44" t="n">
+        <v>61</v>
+      </c>
+      <c r="AF56" s="44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="AD57" s="44" t="inlineStr">
+        <is>
+          <t>5.1 Cut-over runbook: one A-record, MX untouchab</t>
+        </is>
+      </c>
+      <c r="AE57" s="44" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF57" s="44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="AD58" s="44" t="inlineStr">
+        <is>
+          <t>4.4 Retest and closure</t>
+        </is>
+      </c>
+      <c r="AE58" s="44" t="n">
+        <v>66</v>
+      </c>
+      <c r="AF58" s="44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="AD59" s="44" t="inlineStr">
+        <is>
+          <t>4.5 Audit clearance documentation</t>
+        </is>
+      </c>
+      <c r="AE59" s="44" t="n">
+        <v>67</v>
+      </c>
+      <c r="AF59" s="44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="AD60" s="44" t="inlineStr">
+        <is>
+          <t>P.3b Documentation, SOPs and handover — Stage 2</t>
+        </is>
+      </c>
+      <c r="AE60" s="44" t="n">
+        <v>67</v>
+      </c>
+      <c r="AF60" s="44" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="AD61" s="44" t="inlineStr">
+        <is>
+          <t>5.2 Redirect layer live; every row asserted auto</t>
+        </is>
+      </c>
+      <c r="AE61" s="44" t="n">
+        <v>68</v>
+      </c>
+      <c r="AF61" s="44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="AD62" s="44" t="inlineStr">
+        <is>
+          <t>5.4 IGOD refresh and India Portal depository rec</t>
+        </is>
+      </c>
+      <c r="AE62" s="44" t="n">
+        <v>69</v>
+      </c>
+      <c r="AF62" s="44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="AD63" s="44" t="inlineStr">
+        <is>
+          <t>5.3 Sitemap, robots and Search Console submissio</t>
+        </is>
+      </c>
+      <c r="AE63" s="44" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF63" s="44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="AD64" s="44" t="inlineStr">
+        <is>
+          <t>5.5 Hypercare and 404-log review</t>
+        </is>
+      </c>
+      <c r="AE64" s="44" t="n">
+        <v>71</v>
+      </c>
+      <c r="AF64" s="44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="AD70" s="73" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="AE70" s="73" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="AF70" s="73" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="AG70" s="73" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="AH70" s="73" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="AI70" s="73" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="AJ70" s="73" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="AK70" s="73" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="AL70" s="73" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="AM70" s="73" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="AN70" s="73" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="AO70" s="73" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="AP70" s="73" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="AQ70" s="73" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="AR70" s="73" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="AS70" s="73" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="AT70" s="73" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="AU70" s="73" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="AV70" s="73" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="AW70" s="73" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="AD71" s="44" t="inlineStr">
+        <is>
+          <t>Migration Engineer</t>
+        </is>
+      </c>
+      <c r="AE71" s="44" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AF71" s="44" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="AG71" s="44" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AH71" s="44" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="AI71" s="44" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="AJ71" s="44" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AK71" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="44" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO71" s="44" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="AP71" s="44" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="AQ71" s="44" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="AR71" s="44" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AS71" s="44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT71" s="44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU71" s="44" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AV71" s="44" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="AW71" s="44" t="n">
+        <v>6.53</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="AD72" s="44" t="inlineStr">
+        <is>
+          <t>Content Strategist / Business Analyst</t>
+        </is>
+      </c>
+      <c r="AE72" s="44" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AF72" s="44" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="AG72" s="44" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="AH72" s="44" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="AI72" s="44" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="AJ72" s="44" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK72" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL72" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM72" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN72" s="44" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="AO72" s="44" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="AP72" s="44" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AQ72" s="44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AR72" s="44" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AS72" s="44" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AT72" s="44" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AU72" s="44" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AV72" s="44" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="AW72" s="44" t="n">
+        <v>6.51</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="AD73" s="44" t="inlineStr">
+        <is>
+          <t>Engagement Lead / Programme Manager</t>
+        </is>
+      </c>
+      <c r="AE73" s="44" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="AF73" s="44" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="AG73" s="44" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="AH73" s="44" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AI73" s="44" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ73" s="44" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AK73" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="44" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AO73" s="44" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AP73" s="44" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AQ73" s="44" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AR73" s="44" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AS73" s="44" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AT73" s="44" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU73" s="44" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AV73" s="44" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AW73" s="44" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="AD74" s="44" t="inlineStr">
+        <is>
+          <t>Solution Architect — Gov.In CMS / DBIM</t>
+        </is>
+      </c>
+      <c r="AE74" s="44" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AF74" s="44" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="AG74" s="44" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AH74" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="44" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="AO74" s="44" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="AP74" s="44" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ74" s="44" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR74" s="44" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AS74" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT74" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU74" s="44" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AV74" s="44" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AW74" s="44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="AD75" s="44" t="inlineStr">
+        <is>
+          <t>Security Engineer</t>
+        </is>
+      </c>
+      <c r="AE75" s="44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF75" s="44" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="AG75" s="44" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AH75" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR75" s="44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AS75" s="44" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AT75" s="44" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="AU75" s="44" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="AV75" s="44" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AW75" s="44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="AD76" s="44" t="inlineStr">
+        <is>
+          <t>Content Operations / Editorial support</t>
+        </is>
+      </c>
+      <c r="AE76" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="44" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG76" s="44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH76" s="44" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AI76" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL76" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="44" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AP76" s="44" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AQ76" s="44" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="AR76" s="44" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AS76" s="44" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT76" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV76" s="44" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AW76" s="44" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="AD77" s="44" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="AE77" s="44" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF77" s="44" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG77" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="44" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP77" s="44" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ77" s="44" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AR77" s="44" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AS77" s="44" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AT77" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV77" s="44" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AW77" s="44" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="AD78" s="44" t="inlineStr">
+        <is>
+          <t>Accessibility Specialist</t>
+        </is>
+      </c>
+      <c r="AE78" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG78" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI78" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL78" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM78" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN78" s="44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO78" s="44" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AP78" s="44" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ78" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR78" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS78" s="44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT78" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV78" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW78" s="44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="AD79" s="23" t="inlineStr">
+        <is>
+          <t>Total FTE</t>
+        </is>
+      </c>
+      <c r="AE79" s="44" t="n">
+        <v>1.382</v>
+      </c>
+      <c r="AF79" s="44" t="n">
+        <v>2.766</v>
+      </c>
+      <c r="AG79" s="44" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="AH79" s="44" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI79" s="44" t="n">
+        <v>1.455</v>
+      </c>
+      <c r="AJ79" s="44" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="AK79" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL79" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM79" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN79" s="44" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="AO79" s="44" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="AP79" s="44" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="AQ79" s="44" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="AR79" s="44" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="AS79" s="44" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="AT79" s="44" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="AU79" s="44" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AV79" s="44" t="n">
+        <v>1.506</v>
+      </c>
+      <c r="AW79" s="44" t="n">
+        <v>0.954</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
